--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260617_215432.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260617_215432.xlsx
@@ -5858,7 +5858,7 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6006,7 +6006,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6162,7 +6162,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -8390,7 +8390,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8466,7 +8466,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8534,7 +8534,7 @@
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
